--- a/site/exports/csu-physics.xlsx
+++ b/site/exports/csu-physics.xlsx
@@ -2854,7 +2854,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Junwei Fu", "source_url": "https://faculty.csu.edu.cn/~m2INBz/zh_CN/index.htm", "source_locator": "L79"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Junwei Fu", "source_url": "https://faculty.csu.edu.cn/~m2INBz/zh_CN/index.htm", "source_locator": "个人主页中题名《Theoretical Insights into the Selectivity of Single-Atom Fe–N–C Catalysts for Electrochemical NOx Reduction》的书目条目"}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Junwei Fu", "source_url": "https://faculty.csu.edu.cn/~m2INBz/zh_CN/index.htm", "source_locator": "L80"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Junwei Fu", "source_url": "https://faculty.csu.edu.cn/~m2INBz/zh_CN/index.htm", "source_locator": "个人主页中题名《Sustainable conversion of alkaline nitrate to ammonia at activities greater than 2 A cm-2》的书目条目"}</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Ai-Min Guo", "source_url": "https://faculty.csu.edu.cn/guoaimin/zh_CN/index.htm", "source_locator": "L60"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Ai-Min Guo", "source_url": "https://faculty.csu.edu.cn/guoaimin/zh_CN/index.htm", "source_locator": "个人主页中题名《Spin-to-charge conversion driven by inverse chiral-induced spin selectivity》的书目条目"}</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Ai-Min Guo", "source_url": "https://faculty.csu.edu.cn/guoaimin/zh_CN/index.htm", "source_locator": "L61"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Ai-Min Guo", "source_url": "https://faculty.csu.edu.cn/guoaimin/zh_CN/index.htm", "source_locator": "个人主页中题名《Spin-driven Enantioselective Regulation of Cyclooxygenase-2 Activity for Rheumatoid Arthritis Therapy via Chiral Gold Nanohelices》的书目条目"}</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Guang-hua Guo", "source_url": "https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm", "source_locator": "L71"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Guang-hua Guo", "source_url": "https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm", "source_locator": "个人主页中题名《Manipulation of the polarized magnon transmission in trilayer magnonic spin-valve》的书目条目"}</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Guang-hua Guo", "source_url": "https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm", "source_locator": "L73"}</t>
+          <t>{"status": "listed_in_official_personal_bibliography", "matched_author": "Guang-hua Guo", "source_url": "https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm", "source_locator": "个人主页中题名《Reconfigurable Spin-wave Coupler Based on Domain Wall Channels》的书目条目"}</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">

--- a/site/exports/csu-physics.xlsx
+++ b/site/exports/csu-physics.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业资料，学历、导师与时间线仍有未决项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：固体物理；国家精品课程和国家精品资源共享课程负责人；教学／课程开设时间：时间未披露；课程建设职责，不是本人教育/学位事件；时间未披露。；来源ID：csu-guoguanghua-profile；https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm</t>
+          <t>分批核实资料，不是完整名录；部分公开职业资料，学历、导师与时间线仍有未决项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：固体物理；国家精品课程和国家精品资源共享课程负责人；教学／课程开设时间：时间未披露；课程建设职责，不是本人教育/学位事件；时间未披露。；来源ID：csu-guoguanghua-profile；https://faculty.csu.edu.cn/guoguanghua/zh_CN/index.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
